--- a/docs/test-data/第三周教学班学生关联导入合法测试数据.xlsx
+++ b/docs/test-data/第三周教学班学生关联导入合法测试数据.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,160 +431,170 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>学号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>专业代码</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>入学年份</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>教学班编号</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>20220101001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>周一帆</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>080901</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>TC2024CS01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>20220101011</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>080901</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>TC2024CS01</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>20220101021</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>孙丽</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>080901</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>TC2024CS02</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>20220101031</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>宋涛</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>080901</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>TC2024CS03</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>20220101041</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>沈璐</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>080901</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>TC2024CS09</t>
         </is>
